--- a/data/source-momento4-planeacion-territorial/Experiencia_ _Transformaciones que nos conectan_. (UC TRANSLOCAL)(1-56).xlsx
+++ b/data/source-momento4-planeacion-territorial/Experiencia_ _Transformaciones que nos conectan_. (UC TRANSLOCAL)(1-56).xlsx
@@ -124,10 +124,10 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -176,10 +176,10 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
-        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
-        <a:font script="Hans" typeface="å®ä½"/>
-        <a:font script="Hant" typeface="æ°ç´°æé«"/>
+        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
+        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
+        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
+        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -496,7 +496,7 @@
         <v>46251.803773148145</v>
       </c>
       <c r="D2" t="str">
-        <v>ydmsegovia@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -525,7 +525,7 @@
         <v>46252.40939814815</v>
       </c>
       <c r="D3" t="str">
-        <v>smurciac@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -554,7 +554,7 @@
         <v>46252.410219907404</v>
       </c>
       <c r="D4" t="str">
-        <v>vpenuela@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -586,7 +586,7 @@
         <v>46252.41045138889</v>
       </c>
       <c r="D5" t="str">
-        <v>nxsanchez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -618,7 +618,7 @@
         <v>46252.41076388889</v>
       </c>
       <c r="D6" t="str">
-        <v>sfvergara@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -650,7 +650,7 @@
         <v>46252.416666666664</v>
       </c>
       <c r="D7" t="str">
-        <v>rmunevar@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -676,7 +676,7 @@
         <v>46252.41811342593</v>
       </c>
       <c r="D8" t="str">
-        <v>clorenarodriguez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -708,7 +708,7 @@
         <v>46252.424259259256</v>
       </c>
       <c r="D9" t="str">
-        <v>vnancy@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -740,7 +740,7 @@
         <v>46252.43200231482</v>
       </c>
       <c r="D10" t="str">
-        <v>ncrubio@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -772,7 +772,7 @@
         <v>46252.4369212963</v>
       </c>
       <c r="D11" t="str">
-        <v>nestorjgarcia@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -801,7 +801,7 @@
         <v>46252.43717592592</v>
       </c>
       <c r="D12" t="str">
-        <v>hcastrof@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -830,7 +830,7 @@
         <v>46252.643796296295</v>
       </c>
       <c r="D13" t="str">
-        <v>empachon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -859,7 +859,7 @@
         <v>46252.64381944444</v>
       </c>
       <c r="D14" t="str">
-        <v>hacorredor@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -888,7 +888,7 @@
         <v>46252.64387731482</v>
       </c>
       <c r="D15" t="str">
-        <v>ccpachon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -917,7 +917,7 @@
         <v>46252.644953703704</v>
       </c>
       <c r="D16" t="str">
-        <v>jcarinagomez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -949,7 +949,7 @@
         <v>46252.64512731481</v>
       </c>
       <c r="D17" t="str">
-        <v>rguilombo@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -978,7 +978,7 @@
         <v>46252.645150462966</v>
       </c>
       <c r="D18" t="str">
-        <v>hamontano@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1007,7 +1007,7 @@
         <v>46252.64673611111</v>
       </c>
       <c r="D19" t="str">
-        <v>yandreyrincon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1036,7 +1036,7 @@
         <v>46252.65545138889</v>
       </c>
       <c r="D20" t="str">
-        <v>yessicatrodriguez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1065,7 +1065,7 @@
         <v>46252.65608796296</v>
       </c>
       <c r="D21" t="str">
-        <v>nleonr@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1094,7 +1094,7 @@
         <v>46252.656226851854</v>
       </c>
       <c r="D22" t="str">
-        <v>jcforigua@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>46252.65635416667</v>
       </c>
       <c r="D23" t="str">
-        <v>lncajamarca@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1155,7 +1155,7 @@
         <v>46252.65644675926</v>
       </c>
       <c r="D24" t="str">
-        <v>paulaaperez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1184,7 +1184,7 @@
         <v>46252.65646990741</v>
       </c>
       <c r="D25" t="str">
-        <v>kxvillamil@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1213,7 +1213,7 @@
         <v>46252.65684027778</v>
       </c>
       <c r="D26" t="str">
-        <v>angiecrojas@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1245,7 +1245,7 @@
         <v>46252.65792824074</v>
       </c>
       <c r="D27" t="str">
-        <v>krociomurcia@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1277,7 +1277,7 @@
         <v>46252.664039351854</v>
       </c>
       <c r="D28" t="str">
-        <v>yzsantana@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1306,7 +1306,7 @@
         <v>46252.66458333333</v>
       </c>
       <c r="D29" t="str">
-        <v>hcarolinasierra@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1335,7 +1335,7 @@
         <v>46252.66501157408</v>
       </c>
       <c r="D30" t="str">
-        <v>vjcastro@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1367,7 +1367,7 @@
         <v>46252.66599537037</v>
       </c>
       <c r="D31" t="str">
-        <v>jalayon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1396,7 +1396,7 @@
         <v>46252.66601851852</v>
       </c>
       <c r="D32" t="str">
-        <v>nmhuertas@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1428,7 +1428,7 @@
         <v>46252.66643518519</v>
       </c>
       <c r="D33" t="str">
-        <v>ndalarcon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1457,7 +1457,7 @@
         <v>46252.674097222225</v>
       </c>
       <c r="D34" t="str">
-        <v>dalwjandrochaves@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1486,7 +1486,7 @@
         <v>46252.67420138889</v>
       </c>
       <c r="D35" t="str">
-        <v>nalavardo@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1518,7 +1518,7 @@
         <v>46252.67453703703</v>
       </c>
       <c r="D36" t="str">
-        <v>danielssuarez@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1550,7 +1550,7 @@
         <v>46252.67486111111</v>
       </c>
       <c r="D37" t="str">
-        <v>ynmolina@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1582,7 +1582,7 @@
         <v>46252.67569444444</v>
       </c>
       <c r="D38" t="str">
-        <v>jbriseno@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1614,7 +1614,7 @@
         <v>46252.680231481485</v>
       </c>
       <c r="D39" t="str">
-        <v>eestibengarzon@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1643,7 +1643,7 @@
         <v>46252.68082175926</v>
       </c>
       <c r="D40" t="str">
-        <v>ahvanegas@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1672,7 +1672,7 @@
         <v>46252.68085648148</v>
       </c>
       <c r="D41" t="str">
-        <v>karendortiz@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1704,7 +1704,7 @@
         <v>46252.68436342593</v>
       </c>
       <c r="D42" t="str">
-        <v>jprocha@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1736,7 +1736,7 @@
         <v>46252.684652777774</v>
       </c>
       <c r="D43" t="str">
-        <v>kaprada@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -1765,7 +1765,7 @@
         <v>46252.685</v>
       </c>
       <c r="D44" t="str">
-        <v>atota@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -1797,7 +1797,7 @@
         <v>46252.80798611111</v>
       </c>
       <c r="D45" t="str">
-        <v>erpena@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -1832,7 +1832,7 @@
         <v>46252.809641203705</v>
       </c>
       <c r="D46" t="str">
-        <v>jpaolacastiblanco@ucundinamarca.edu.co</v>
+        <v/>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -1867,7 +1867,7 @@
         <v>46252.81890046296</v>
       </c>
       <c r="D47" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I47" t="str">
         <v>Graduados</v>
@@ -1896,7 +1896,7 @@
         <v>46252.819560185184</v>
       </c>
       <c r="D48" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I48" t="str">
         <v>Graduados</v>
@@ -1928,7 +1928,7 @@
         <v>46252.81988425926</v>
       </c>
       <c r="D49" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I49" t="str">
         <v>Graduados</v>
@@ -1960,7 +1960,7 @@
         <v>46252.82864583333</v>
       </c>
       <c r="D50" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I50" t="str">
         <v>Graduados</v>
@@ -1992,7 +1992,7 @@
         <v>46252.82864583333</v>
       </c>
       <c r="D51" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I51" t="str">
         <v>Graduados</v>
@@ -2024,7 +2024,7 @@
         <v>46252.8287037037</v>
       </c>
       <c r="D52" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I52" t="str">
         <v>Graduados</v>
@@ -2056,7 +2056,7 @@
         <v>46252.83876157407</v>
       </c>
       <c r="D53" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I53" t="str">
         <v>Graduados</v>
@@ -2085,7 +2085,7 @@
         <v>46252.8390625</v>
       </c>
       <c r="D54" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I54" t="str">
         <v>Graduados</v>
@@ -2117,7 +2117,7 @@
         <v>46252.84185185185</v>
       </c>
       <c r="D55" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I55" t="str">
         <v>Graduados</v>
@@ -2149,7 +2149,7 @@
         <v>46252.8443287037</v>
       </c>
       <c r="D56" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I56" t="str">
         <v>Graduados</v>
@@ -2181,7 +2181,7 @@
         <v>46252.84452546296</v>
       </c>
       <c r="D57" t="str">
-        <v>anonymous</v>
+        <v/>
       </c>
       <c r="I57" t="str">
         <v>Creadores de Oportunidades (estudiantes)</v>
